--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR VALVULA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR VALVULA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR)  MOTOPORT FAZER150 1104697</t>
+          <t>RETENTOR VALVULA (PAR)  MOTOPORT FAZER150 1104697</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR)  MOTOPORT TITAN CG150 1104694</t>
+          <t>RETENTOR VALVULA (PAR)  MOTOPORT TITAN CG150 1104694</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR)  MOTOPORT FAZER250 1104696</t>
+          <t>RETENTOR VALVULA (PAR)  MOTOPORT FAZER250 1104696</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR)  MOTOPORT TITAN CG125 2001 1104693</t>
+          <t>RETENTOR VALVULA (PAR)  MOTOPORT TITAN CG125 2001 1104693</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR)  MOTOPORT TITAN CG150 1104691</t>
+          <t>RETENTOR VALVULA (PAR)  MOTOPORT TITAN CG150 1104691</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RETENTOR VALV TMAC EN125/ YES125 2005 A 2008 TM078</t>
+          <t>RETENTOR VALVULA TMAC EN125/ YES125 2005 A 2008 TM078</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RETENTOR VALV (PAR) CORTECO TITAN CG125/ BROS NXR125/ BIZ100/ YBR125 CBX250 TWISTER</t>
+          <t>RETENTOR VALVULA (PAR) CORTECO TITAN CG125/ BROS NXR125/ BIZ100/ YBR125 CBX250 TWISTER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RETENTOR VALV PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR125/ CB500</t>
+          <t>RETENTOR VALVULA PEÇA+ FAZER150/ CROSSER XTZ150/ FACTOR125/ CB500</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RETENTOR VALV HONDA </t>
+          <t xml:space="preserve">RETENTOR VALVULA HONDA </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETENTOR VALV IRON TITAN FAN CG150/ CBX250 TWISTER 11059352</t>
+          <t>RETENTOR VALVULA IRON TITAN FAN CG150/ CBX250 TWISTER 11059352</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR VALVULA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR VALVULA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,7 +592,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +612,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,7 +632,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
